--- a/output/roomself_excel/1651.xlsx
+++ b/output/roomself_excel/1651.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>106592</v>
+        <v>128502</v>
       </c>
       <c r="D2" t="n">
-        <v>2640</v>
+        <v>3319</v>
       </c>
       <c r="E2" t="n">
-        <v>731</v>
+        <v>621</v>
       </c>
       <c r="F2" t="n">
-        <v>175</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>246931</v>
+        <v>403488</v>
       </c>
       <c r="D3" t="n">
-        <v>6472</v>
+        <v>6524</v>
       </c>
       <c r="E3" t="n">
-        <v>968</v>
+        <v>792</v>
       </c>
       <c r="F3" t="n">
-        <v>922</v>
+        <v>771</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>531990</v>
+        <v>106592</v>
       </c>
       <c r="D4" t="n">
-        <v>8906</v>
+        <v>2640</v>
       </c>
       <c r="E4" t="n">
-        <v>1464</v>
+        <v>354</v>
       </c>
       <c r="F4" t="n">
-        <v>921</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5">
@@ -542,7 +542,7 @@
         <v>2712</v>
       </c>
       <c r="E5" t="n">
-        <v>770</v>
+        <v>489</v>
       </c>
       <c r="F5" t="n">
         <v>389</v>
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46768</v>
+        <v>139755</v>
       </c>
       <c r="D6" t="n">
-        <v>1816</v>
+        <v>2992</v>
       </c>
       <c r="E6" t="n">
-        <v>321</v>
+        <v>771</v>
       </c>
       <c r="F6" t="n">
-        <v>183</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>139755</v>
+        <v>107508</v>
       </c>
       <c r="D7" t="n">
-        <v>2992</v>
+        <v>2644</v>
       </c>
       <c r="E7" t="n">
-        <v>771</v>
+        <v>422</v>
       </c>
       <c r="F7" t="n">
-        <v>363</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>45815</v>
+        <v>14790</v>
       </c>
       <c r="D9" t="n">
-        <v>1728</v>
+        <v>1036</v>
       </c>
       <c r="E9" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>69335</v>
+        <v>18348</v>
       </c>
       <c r="D10" t="n">
-        <v>2112</v>
+        <v>1084</v>
       </c>
       <c r="E10" t="n">
-        <v>770</v>
+        <v>132</v>
       </c>
       <c r="F10" t="n">
-        <v>283</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14790</v>
+        <v>37113</v>
       </c>
       <c r="D11" t="n">
-        <v>1036</v>
+        <v>1624</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>31236</v>
+        <v>33499</v>
       </c>
       <c r="D12" t="n">
-        <v>1480</v>
+        <v>1520</v>
       </c>
       <c r="E12" t="n">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="F12" t="n">
-        <v>205</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33216</v>
+        <v>46768</v>
       </c>
       <c r="D13" t="n">
-        <v>1460</v>
+        <v>1816</v>
       </c>
       <c r="E13" t="n">
-        <v>192</v>
+        <v>321</v>
       </c>
       <c r="F13" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27507</v>
+        <v>45815</v>
       </c>
       <c r="D14" t="n">
-        <v>1328</v>
+        <v>1728</v>
       </c>
       <c r="E14" t="n">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25752</v>
+        <v>33216</v>
       </c>
       <c r="D15" t="n">
-        <v>1288</v>
+        <v>1460</v>
       </c>
       <c r="E15" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="F15" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37113</v>
+        <v>25752</v>
       </c>
       <c r="D16" t="n">
-        <v>1624</v>
+        <v>1288</v>
       </c>
       <c r="E16" t="n">
-        <v>294</v>
+        <v>177</v>
       </c>
       <c r="F16" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18348</v>
+        <v>246931</v>
       </c>
       <c r="D17" t="n">
-        <v>1084</v>
+        <v>6472</v>
       </c>
       <c r="E17" t="n">
-        <v>132</v>
+        <v>513</v>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>33499</v>
+        <v>69335</v>
       </c>
       <c r="D18" t="n">
-        <v>1520</v>
+        <v>2112</v>
       </c>
       <c r="E18" t="n">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="F18" t="n">
-        <v>175</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>107508</v>
+        <v>31236</v>
       </c>
       <c r="D19" t="n">
-        <v>2644</v>
+        <v>1480</v>
       </c>
       <c r="E19" t="n">
-        <v>422</v>
+        <v>215</v>
       </c>
       <c r="F19" t="n">
-        <v>150</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,38 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>27507</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1328</v>
+      </c>
+      <c r="E20" t="n">
+        <v>159</v>
+      </c>
+      <c r="F20" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>103880</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>2604</v>
       </c>
-      <c r="E20" t="n">
-        <v>797</v>
-      </c>
-      <c r="F20" t="n">
-        <v>177</v>
+      <c r="E21" t="n">
+        <v>421</v>
+      </c>
+      <c r="F21" t="n">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/1651.xlsx
+++ b/output/roomself_excel/1651.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,34 @@
       <c r="D2" t="n">
         <v>3319</v>
       </c>
-      <c r="E2" t="n">
-        <v>621</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>347</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>408</v>
+      </c>
+      <c r="J2" t="n">
+        <v>27</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +569,42 @@
       <c r="D3" t="n">
         <v>6524</v>
       </c>
-      <c r="E3" t="n">
-        <v>792</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>771</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>251</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>68</v>
+      </c>
+      <c r="M3" t="n">
+        <v>26</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +621,34 @@
       <c r="D4" t="n">
         <v>2640</v>
       </c>
-      <c r="E4" t="n">
-        <v>354</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>151</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>126</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +665,34 @@
       <c r="D5" t="n">
         <v>2712</v>
       </c>
-      <c r="E5" t="n">
-        <v>489</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>389</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>314</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +709,34 @@
       <c r="D6" t="n">
         <v>2992</v>
       </c>
-      <c r="E6" t="n">
-        <v>771</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>363</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>385</v>
+      </c>
+      <c r="J6" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +753,34 @@
       <c r="D7" t="n">
         <v>2644</v>
       </c>
-      <c r="E7" t="n">
-        <v>422</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>150</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="G7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>372</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +797,34 @@
       <c r="D8" t="n">
         <v>3368</v>
       </c>
-      <c r="E8" t="n">
-        <v>772</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>387</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>159</v>
+      </c>
+      <c r="J8" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +841,18 @@
       <c r="D9" t="n">
         <v>1036</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +869,26 @@
       <c r="D10" t="n">
         <v>1084</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>132</v>
       </c>
-      <c r="F10" t="n">
-        <v>25</v>
-      </c>
+      <c r="G10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +905,34 @@
       <c r="D11" t="n">
         <v>1624</v>
       </c>
-      <c r="E11" t="n">
-        <v>294</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>164</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="G11" t="n">
+        <v>27</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>267</v>
+      </c>
+      <c r="J11" t="n">
+        <v>25</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +949,26 @@
       <c r="D12" t="n">
         <v>1520</v>
       </c>
-      <c r="E12" t="n">
-        <v>241</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>175</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="G12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +985,34 @@
       <c r="D13" t="n">
         <v>1816</v>
       </c>
-      <c r="E13" t="n">
-        <v>321</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>183</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="G13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>158</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1029,34 @@
       <c r="D14" t="n">
         <v>1728</v>
       </c>
-      <c r="E14" t="n">
-        <v>270</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>212</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="G14" t="n">
+        <v>25</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>187</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1073,26 @@
       <c r="D15" t="n">
         <v>1460</v>
       </c>
-      <c r="E15" t="n">
-        <v>192</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>175</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="G15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1109,26 @@
       <c r="D16" t="n">
         <v>1288</v>
       </c>
-      <c r="E16" t="n">
-        <v>177</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>174</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="G16" t="n">
+        <v>25</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,11 +1145,49 @@
       <c r="D17" t="n">
         <v>6472</v>
       </c>
-      <c r="E17" t="n">
-        <v>513</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>397</v>
+        <v>372</v>
+      </c>
+      <c r="G17" t="n">
+        <v>25</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>125</v>
+      </c>
+      <c r="J17" t="n">
+        <v>25</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>40</v>
+      </c>
+      <c r="M17" t="n">
+        <v>35</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>34</v>
+      </c>
+      <c r="P17" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -827,12 +1205,26 @@
       <c r="D18" t="n">
         <v>2112</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>283</v>
       </c>
-      <c r="F18" t="n">
-        <v>25</v>
-      </c>
+      <c r="G18" t="n">
+        <v>25</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1241,34 @@
       <c r="D19" t="n">
         <v>1480</v>
       </c>
-      <c r="E19" t="n">
-        <v>215</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>205</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="G19" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>180</v>
+      </c>
+      <c r="J19" t="n">
+        <v>25</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1285,34 @@
       <c r="D20" t="n">
         <v>1328</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>173</v>
+      </c>
+      <c r="G20" t="n">
+        <v>25</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>159</v>
       </c>
-      <c r="F20" t="n">
-        <v>25</v>
-      </c>
+      <c r="J20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1329,34 @@
       <c r="D21" t="n">
         <v>2604</v>
       </c>
-      <c r="E21" t="n">
-        <v>421</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>152</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="G21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>371</v>
+      </c>
+      <c r="J21" t="n">
+        <v>25</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
